--- a/public/Personnel.xlsx
+++ b/public/Personnel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852037FC-2E78-4BB1-8F1F-1DC74D251586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B1C133-61F8-4A17-8271-07F165C0CCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{6C68B563-5BA5-47BD-9047-34E37888319D}"/>
   </bookViews>
@@ -147,9 +147,6 @@
     <t>Lovelyn Correa-Quering</t>
   </si>
   <si>
-    <t>Dianna G. Pacaldo</t>
-  </si>
-  <si>
     <t>Development Management Officer II</t>
   </si>
   <si>
@@ -160,6 +157,9 @@
   </si>
   <si>
     <t>Queenie Faye P. Pahit</t>
+  </si>
+  <si>
+    <t>Diana G. Pacaldo</t>
   </si>
 </sst>
 </file>
@@ -710,7 +710,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>19</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>33</v>
@@ -765,7 +765,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -776,7 +776,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
@@ -784,10 +784,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>

--- a/public/Personnel.xlsx
+++ b/public/Personnel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B1C133-61F8-4A17-8271-07F165C0CCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA57659F-BFB3-40A4-995D-53E4098EF65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{6C68B563-5BA5-47BD-9047-34E37888319D}"/>
   </bookViews>

--- a/public/Personnel.xlsx
+++ b/public/Personnel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA57659F-BFB3-40A4-995D-53E4098EF65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE89C061-721A-4BEA-B2BD-FDD553AAD4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{6C68B563-5BA5-47BD-9047-34E37888319D}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>Computer Programmer</t>
   </si>
   <si>
-    <t>Admin Assistant II</t>
-  </si>
-  <si>
     <t>Project Development Officer II</t>
   </si>
   <si>
@@ -160,6 +157,9 @@
   </si>
   <si>
     <t>Diana G. Pacaldo</t>
+  </si>
+  <si>
+    <t>Administrative Assistant VI</t>
   </si>
 </sst>
 </file>
@@ -564,13 +564,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -578,10 +578,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -589,10 +589,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -603,7 +603,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -614,7 +614,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -622,10 +622,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -633,10 +633,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
@@ -644,10 +644,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
@@ -655,10 +655,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -666,10 +666,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -677,10 +677,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -688,10 +688,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -699,131 +699,131 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/public/Personnel.xlsx
+++ b/public/Personnel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE89C061-721A-4BEA-B2BD-FDD553AAD4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF260E6-CCD6-4D89-9671-DF9FB5A4BFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{6C68B563-5BA5-47BD-9047-34E37888319D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>Name</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Administrative Assistant VI</t>
+  </si>
+  <si>
+    <t>Francis Irene C. Limbaga</t>
   </si>
 </sst>
 </file>
@@ -197,7 +200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -220,15 +223,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE138591-2086-4980-893B-7DCAF58AB13F}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.3984375" customWidth="1"/>
@@ -826,6 +841,17 @@
         <v>24</v>
       </c>
     </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
